--- a/output/pdf_financials_xlsx/LUG.xlsx
+++ b/output/pdf_financials_xlsx/LUG.xlsx
@@ -919,19 +919,19 @@
         <v>5.607</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>42.657</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>46.458</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>51.934</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>69.158</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>102.819</v>
       </c>
     </row>
     <row r="10">
@@ -1325,34 +1325,34 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>12.66708</v>
+        <v>-12.66708</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.013329</v>
+        <v>-1.013329</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.463735</v>
+        <v>-0.463735</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.259416</v>
+        <v>-0.259416</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.7487239999999999</v>
+        <v>-0.7487239999999999</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>45.323862</v>
+        <v>-45.323862</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>62.814</v>
+        <v>-62.814</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>41.14</v>
+        <v>-41.14</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22.068</v>
+        <v>-22.068</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>118.945</v>
+        <v>-118.945</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>257.101</v>
@@ -1633,34 +1633,34 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.66708</v>
+        <v>-12.66708</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.013329</v>
+        <v>-1.013329</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.463735</v>
+        <v>-0.463735</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.259416</v>
+        <v>-0.259416</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.7487239999999999</v>
+        <v>-0.7487239999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>45.323862</v>
+        <v>-45.323862</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>62.814</v>
+        <v>-62.814</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>41.14</v>
+        <v>-41.14</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>22.068</v>
+        <v>-22.068</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>118.945</v>
+        <v>-118.945</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>355.712</v>
@@ -1819,34 +1819,34 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>12.66708</v>
+        <v>-12.66708</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.013329</v>
+        <v>-1.013329</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.463735</v>
+        <v>-0.463735</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.259416</v>
+        <v>-0.259416</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.7487239999999999</v>
+        <v>-0.7487239999999999</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>45.323862</v>
+        <v>-45.323862</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>62.814</v>
+        <v>-62.814</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>41.14</v>
+        <v>-41.14</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>22.068</v>
+        <v>-22.068</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>118.945</v>
+        <v>-118.945</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>221.426</v>
@@ -2005,34 +2005,34 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>9.179043</v>
+        <v>-9.179043</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>14.476129</v>
+        <v>-14.476129</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>15.457833</v>
+        <v>-15.457833</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.9708</v>
+        <v>-12.9708</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18.7181</v>
+        <v>-18.7181</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>100.719693</v>
+        <v>-100.719693</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>108.3</v>
+        <v>-108.3</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>117.542857</v>
+        <v>-117.542857</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>183.9</v>
+        <v>-183.9</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>220.268519</v>
+        <v>-220.268519</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>234.576889</v>
@@ -2067,34 +2067,34 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>12.66708</v>
+        <v>-12.66708</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.013329</v>
+        <v>-1.013329</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.463735</v>
+        <v>-0.463735</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.259416</v>
+        <v>-0.259416</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.7487239999999999</v>
+        <v>-0.7487239999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>45.323862</v>
+        <v>-45.323862</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>62.814</v>
+        <v>-62.814</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>41.14</v>
+        <v>-41.14</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>22.068</v>
+        <v>-22.068</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>118.945</v>
+        <v>-118.945</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>257.101</v>
@@ -2191,34 +2191,34 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.66708</v>
+        <v>-12.66708</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.013329</v>
+        <v>-1.013329</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.463735</v>
+        <v>-0.463735</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.259416</v>
+        <v>-0.259416</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.777458</v>
+        <v>-0.71999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>45.323862</v>
+        <v>-45.323862</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>62.814</v>
+        <v>-62.814</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>41.213</v>
+        <v>-41.067</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>22.191</v>
+        <v>-21.945</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>119.075</v>
+        <v>-118.815</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>364.66</v>
@@ -2337,34 +2337,34 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>23.22900338777368</v>
@@ -5901,13 +5901,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.006547</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.006547</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.851316</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>-2.839998</v>
@@ -5956,49 +5956,49 @@
         <v>1.713562</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.918543</v>
+        <v>1.793995</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.032904</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.230113</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.195716</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.006381</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.012391</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.422</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.547000000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>12.125</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>14.118</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>13.57</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>13.856</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.535</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>9.058999999999999</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.621</v>
       </c>
     </row>
     <row r="93">
@@ -10608,7 +10608,11 @@
           <t>Equity-settled share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -13845,7 +13849,11 @@
           <t>Equity-settled share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -15047,7 +15055,11 @@
           <t>Equity-settled share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -15439,7 +15451,11 @@
           <t>Equity-settled share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -15635,7 +15651,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -16126,7 +16146,11 @@
           <t>Equity-settled share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -16219,7 +16243,11 @@
           <t>Foreign currency translation reserve 8</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -17130,7 +17158,11 @@
           <t>Equity-settled share-based payment reserve 8 2,032,904</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -17225,7 +17257,11 @@
           <t>Foreign currency translation reserve 9 6,547</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -32071,7 +32107,11 @@
           <t>Royalty expenses</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -41811,22 +41851,22 @@
         </is>
       </c>
       <c r="K336" s="5" t="n">
-        <v>0.7487239999999999</v>
+        <v>-0.7487239999999999</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>45.323862</v>
+        <v>-45.323862</v>
       </c>
       <c r="M336" s="5" t="n">
-        <v>62.814</v>
+        <v>-62.814</v>
       </c>
       <c r="N336" s="5" t="n">
-        <v>41.14</v>
+        <v>-41.14</v>
       </c>
       <c r="O336" s="5" t="n">
-        <v>22.068</v>
+        <v>-22.068</v>
       </c>
       <c r="P336" s="5" t="n">
-        <v>118.945</v>
+        <v>-118.945</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -42214,13 +42254,13 @@
         </is>
       </c>
       <c r="N340" s="5" t="n">
-        <v>41.126</v>
+        <v>-41.126</v>
       </c>
       <c r="O340" s="5" t="n">
-        <v>35.806</v>
+        <v>-35.806</v>
       </c>
       <c r="P340" s="5" t="n">
-        <v>175.839</v>
+        <v>-175.839</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -43378,25 +43418,25 @@
         </is>
       </c>
       <c r="H352" s="5" t="n">
-        <v>1.104159</v>
+        <v>-1.104159</v>
       </c>
       <c r="I352" s="5" t="n">
-        <v>0.463735</v>
+        <v>-0.463735</v>
       </c>
       <c r="J352" s="5" t="n">
-        <v>1.736959</v>
+        <v>-1.736959</v>
       </c>
       <c r="K352" s="5" t="n">
-        <v>2.737406</v>
+        <v>-2.737406</v>
       </c>
       <c r="L352" s="5" t="n">
-        <v>53.056563</v>
+        <v>-53.056563</v>
       </c>
       <c r="M352" s="5" t="n">
-        <v>63.619</v>
+        <v>-63.619</v>
       </c>
       <c r="N352" s="5" t="n">
-        <v>41.126</v>
+        <v>-41.126</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -45546,16 +45586,16 @@
         </is>
       </c>
       <c r="H374" s="5" t="n">
-        <v>1.013329</v>
+        <v>-1.013329</v>
       </c>
       <c r="I374" s="5" t="n">
-        <v>0.463735</v>
+        <v>-0.463735</v>
       </c>
       <c r="J374" s="5" t="n">
-        <v>0.259416</v>
+        <v>-0.259416</v>
       </c>
       <c r="K374" s="5" t="n">
-        <v>0.7487239999999999</v>
+        <v>-0.7487239999999999</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -47553,10 +47593,10 @@
         </is>
       </c>
       <c r="G394" s="5" t="n">
-        <v>12.66708</v>
+        <v>-12.66708</v>
       </c>
       <c r="H394" s="5" t="n">
-        <v>1.013329</v>
+        <v>-1.013329</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -47755,10 +47795,10 @@
         </is>
       </c>
       <c r="G396" s="5" t="n">
-        <v>12.569703</v>
+        <v>-12.569703</v>
       </c>
       <c r="H396" s="5" t="n">
-        <v>1.104159</v>
+        <v>-1.104159</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LUG.xlsx
+++ b/output/pdf_financials_xlsx/LUG.xlsx
@@ -1092,22 +1092,22 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.108063</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.18018</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.115</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-4.642</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-1.763</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.353</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>-5.088</v>
@@ -2082,22 +2082,22 @@
         <v>-0.7487239999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-45.323862</v>
+        <v>-45.215799</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-62.814</v>
+        <v>-62.63382</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-41.14</v>
+        <v>-41.025</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-22.068</v>
+        <v>-17.426</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-118.945</v>
+        <v>-117.182</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>257.101</v>
+        <v>257.454</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>182.362</v>
@@ -2206,22 +2206,22 @@
         <v>-0.71999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-45.323862</v>
+        <v>-45.215799</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-62.814</v>
+        <v>-62.63382</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-41.067</v>
+        <v>-40.952</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-21.945</v>
+        <v>-17.303</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-118.815</v>
+        <v>-117.052</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>364.66</v>
+        <v>365.013</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>313.037</v>
@@ -2480,31 +2480,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.188233</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.281037</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.281037</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>23.109638</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>22.834935</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>21.328135</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>70.919477</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>21.360228</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>8.503</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>35.018</v>
@@ -2596,31 +2596,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.188233</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.281037</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.281037</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>23.109638</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>22.834935</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>21.328135</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>70.919477</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>21.360228</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>8.503</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>35.018</v>
@@ -3292,22 +3292,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.927732</v>
+        <v>1.739499</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.560904</v>
+        <v>0.279867</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.560904</v>
+        <v>0.279867</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>23.121951</v>
+        <v>0.012313</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>22.844885</v>
+        <v>0.009950000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>21.335635</v>
+        <v>0.0075</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.72814</v>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -37774,7 +37774,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -39473,7 +39473,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
